--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -1,47 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476640\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8A2E9286-67FF-4070-BC89-5E6F676E5985}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F17B18-9C53-451E-A1EC-31CAB16A486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="24" firstSheet="22" windowHeight="10300" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CVCSPSCFCorp_IPDailyNOP" r:id="rId1" sheetId="1"/>
-    <sheet name="CVCSPSCFCorp_AutomaticPayment" r:id="rId2" sheetId="2"/>
-    <sheet name="CVCSPSCFPC_AutomaticPayment" r:id="rId3" sheetId="4"/>
-    <sheet name="CVCSPSCFPS_AutomaticPayment" r:id="rId4" sheetId="3"/>
-    <sheet name="CVCSPSCFCC_AutomaticPayment" r:id="rId5" sheetId="5"/>
-    <sheet name="CVCSPSCFPS_RecDeferred" r:id="rId6" sheetId="6"/>
-    <sheet name="CVCSPSCFPC_RecDeferred" r:id="rId7" sheetId="7"/>
-    <sheet name="CVCSPSCFCorp_RecDeferred" r:id="rId8" sheetId="8"/>
-    <sheet name="CVCSPSCFCC_RecDeferred" r:id="rId9" sheetId="9"/>
-    <sheet name="CVCSPSCFPS_RecDaily" r:id="rId10" sheetId="10"/>
-    <sheet name="CVCSPSCFPC_RecDaily" r:id="rId11" sheetId="11"/>
-    <sheet name="CVCSPSCFCorp_RecDaily" r:id="rId12" sheetId="12"/>
-    <sheet name="CVCSPSCFCC_RecDaily" r:id="rId13" sheetId="13"/>
-    <sheet name="CVCSPSCFPS_IPDeferred" r:id="rId14" sheetId="14"/>
-    <sheet name="CVCSPSCFPC_IPDeferred" r:id="rId15" sheetId="15"/>
-    <sheet name="CVCSPSCFCC_IPDeferred" r:id="rId16" sheetId="16"/>
-    <sheet name="CVCSPSCFCorp_IPDeferred" r:id="rId17" sheetId="17"/>
-    <sheet name="CVCSPSCFPS_IPDailyIA" r:id="rId18" sheetId="18"/>
-    <sheet name="CVCSPSCFPC_IPDailyIA" r:id="rId19" sheetId="19"/>
-    <sheet name="CVCSPSCFCC_IPDailyIA" r:id="rId20" sheetId="20"/>
-    <sheet name="CVCSPSCFCorp_IPDailyIA" r:id="rId21" sheetId="21"/>
-    <sheet name="CVCSPSCFCC_IPDailyNOP" r:id="rId22" sheetId="22"/>
-    <sheet name="CVCSPSCFPC_IPDailyNOP" r:id="rId23" sheetId="23"/>
-    <sheet name="CVCSPSCFPS_IPDailyNOP" r:id="rId24" sheetId="24"/>
-    <sheet name="CVCSPSCFCorp_RecMonthly" r:id="rId25" sheetId="25"/>
+    <sheet name="CVCSPSCFCorp_IPDailyNOP" sheetId="1" r:id="rId1"/>
+    <sheet name="CVCSPSCFCorp_AutomaticPayment" sheetId="2" r:id="rId2"/>
+    <sheet name="CVCSPSCFPC_AutomaticPayment" sheetId="4" r:id="rId3"/>
+    <sheet name="CVCSPSCFPS_AutomaticPayment" sheetId="3" r:id="rId4"/>
+    <sheet name="CVCSPSCFCC_AutomaticPayment" sheetId="5" r:id="rId5"/>
+    <sheet name="CVCSPSCFPS_RecDeferred" sheetId="6" r:id="rId6"/>
+    <sheet name="CVCSPSCFPC_RecDeferred" sheetId="7" r:id="rId7"/>
+    <sheet name="CVCSPSCFCorp_RecDeferred" sheetId="8" r:id="rId8"/>
+    <sheet name="CVCSPSCFCC_RecDeferred" sheetId="9" r:id="rId9"/>
+    <sheet name="CVCSPSCFPS_RecDaily" sheetId="10" r:id="rId10"/>
+    <sheet name="CVCSPSCFPC_RecDaily" sheetId="11" r:id="rId11"/>
+    <sheet name="CVCSPSCFCorp_RecDaily" sheetId="12" r:id="rId12"/>
+    <sheet name="CVCSPSCFCC_RecDaily" sheetId="13" r:id="rId13"/>
+    <sheet name="CVCSPSCFPS_IPDeferred" sheetId="14" r:id="rId14"/>
+    <sheet name="CVCSPSCFPC_IPDeferred" sheetId="15" r:id="rId15"/>
+    <sheet name="CVCSPSCFCC_IPDeferred" sheetId="16" r:id="rId16"/>
+    <sheet name="CVCSPSCFCorp_IPDeferred" sheetId="17" r:id="rId17"/>
+    <sheet name="CVCSPSCFPS_IPDailyIA" sheetId="18" r:id="rId18"/>
+    <sheet name="CVCSPSCFPC_IPDailyIA" sheetId="19" r:id="rId19"/>
+    <sheet name="CVCSPSCFCC_IPDailyIA" sheetId="20" r:id="rId20"/>
+    <sheet name="CVCSPSCFCorp_IPDailyIA" sheetId="21" r:id="rId21"/>
+    <sheet name="CVCSPSCFCC_IPDailyNOP" sheetId="22" r:id="rId22"/>
+    <sheet name="CVCSPSCFPC_IPDailyNOP" sheetId="23" r:id="rId23"/>
+    <sheet name="CVCSPSCFPS_IPDailyNOP" sheetId="24" r:id="rId24"/>
+    <sheet name="CVCSPSCFCorp_RecMonthly" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="72">
   <si>
     <t>Result</t>
   </si>
@@ -126,18 +126,6 @@
   </si>
   <si>
     <t>AutomaticPayment</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 01:06:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 01:10:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 01:16:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 01:27:43 IST 2025</t>
   </si>
   <si>
     <t>RecurringAmount</t>
@@ -316,15 +304,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Sep 16 14:11:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 14:15:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 16 14:20:03 IST 2025</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 180RemittanceID: 917-152027,
 1. Review bill to pay,
@@ -347,9 +326,6 @@
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
 4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 11:51:59 IST 2025</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -453,18 +429,6 @@
 4. Payment Plan, Daily payments of $</t>
   </si>
   <si>
-    <t>Wed Sep 17 14:26:27 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 14:33:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 14:45:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 15:16:37 IST 2025</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 180RemittanceID: 917-152027,
 1. Review bill to pay,
@@ -541,9 +505,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Wed Sep 17 19:37:25 IST 2025</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 180RemittanceID: 917-152027,
 1. Review bill to pay,
@@ -567,15 +528,6 @@
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
 4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 19:40:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 19:43:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 19:46:30 IST 2025</t>
   </si>
   <si>
     <t>IndividualAmount</t>
@@ -682,34 +634,7 @@
 4. Payment Plan,1 Daily payment of $</t>
   </si>
   <si>
-    <t>Wed Sep 17 20:03:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 20:08:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 20:12:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 20:35:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 21:09:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 21:12:18 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 21:14:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 21:16:11 IST 2025</t>
-  </si>
-  <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 18:58:05 IST 2025</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -739,94 +664,79 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:01:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 18:58:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:19:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:21:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:24:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:27:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:29:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:32:13 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:34:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:36:08 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:38:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:42:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:44:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 21:47:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:23:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:25:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:28:12 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:30:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:33:31 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:36:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:38:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:40:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:43:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:45:08 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:47:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:49:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:51:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 22:54:02 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 17 16:20:01 IST 2025</t>
+    <t>Fri Dec 26 21:03:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:04:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:05:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:07:08 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:08:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:09:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:10:52 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:12:08 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:13:42 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:15:15 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:16:43 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:18:09 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:19:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:20:55 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:22:08 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:23:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:25:14 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:26:50 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:28:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:29:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:30:43 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:32:28 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:34:04 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:35:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:37:24 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -895,46 +805,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="164" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -951,10 +861,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -989,7 +899,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1024,7 +934,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1118,21 +1028,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1149,7 +1059,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1201,22 +1111,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" customWidth="true" width="23.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="30.26953125" collapsed="true"/>
+    <col min="7" max="7" width="23.6328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="30.26953125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,12 +1176,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1297,11 +1207,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1335,7 +1245,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1343,13 +1253,13 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1357,14 +1267,14 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="26.08984375" collapsed="true"/>
+    <col min="11" max="11" width="26.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1414,12 +1324,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1436,7 +1346,7 @@
         <v>CarlosJacinta</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -1445,11 +1355,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1481,7 +1391,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 10/16/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1489,25 +1399,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="25.7265625" collapsed="true"/>
+    <col min="11" max="11" width="25.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1557,12 +1467,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1579,7 +1489,7 @@
         <v>Carlos</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -1588,11 +1498,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1624,7 +1534,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 10/16/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1632,25 +1542,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="30.7265625" collapsed="true"/>
+    <col min="11" max="11" width="30.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1700,12 +1610,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1722,7 +1632,7 @@
         <v>Smith</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -1731,11 +1641,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1769,7 +1679,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 10/16/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1777,25 +1687,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="34.7265625" collapsed="true"/>
+    <col min="11" max="11" width="34.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1845,12 +1755,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1867,7 +1777,7 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -1876,11 +1786,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1911,7 +1821,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 10/16/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1919,27 +1829,27 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" width="15.7265625" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" width="17.1796875" collapsed="true"/>
+    <col min="11" max="11" width="24.7265625" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="15.7265625" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="17.1796875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1989,12 +1899,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2014,17 +1924,17 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2056,7 +1966,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2064,25 +1974,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="24.26953125" collapsed="true"/>
+    <col min="11" max="11" width="24.26953125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2132,12 +2042,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2157,17 +2067,17 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2199,7 +2109,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2207,25 +2117,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="23.7265625" collapsed="true"/>
+    <col min="11" max="11" width="23.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2275,12 +2185,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2300,17 +2210,17 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2341,7 +2251,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2349,25 +2259,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="25.81640625" collapsed="true"/>
+    <col min="11" max="11" width="25.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2417,12 +2327,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2442,17 +2352,17 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2486,7 +2396,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2494,25 +2404,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="24.0" collapsed="true"/>
+    <col min="11" max="11" width="24" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2562,12 +2472,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2590,14 +2500,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2629,7 +2539,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2637,25 +2547,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="23.08984375" collapsed="true"/>
+    <col min="11" max="11" width="23.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2705,12 +2615,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2733,14 +2643,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2772,7 +2682,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2780,25 +2690,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="21.90625" collapsed="true"/>
+    <col min="11" max="11" width="21.90625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2848,12 +2758,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2879,11 +2789,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2902,19 +2812,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2964,12 +2874,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2992,14 +2902,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3030,7 +2940,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3038,25 +2948,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
+    <col min="11" max="11" width="20.36328125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3106,12 +3016,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3134,14 +3044,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3175,7 +3085,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3183,25 +3093,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="27.08984375" collapsed="true"/>
+    <col min="11" max="11" width="27.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3251,12 +3161,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3282,11 +3192,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3317,7 +3227,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3325,25 +3235,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="29.0" collapsed="true"/>
+    <col min="11" max="11" width="29" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3393,12 +3303,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3424,11 +3334,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3460,7 +3370,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3468,25 +3378,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
+    <col min="11" max="11" width="29.90625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3536,12 +3446,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3567,11 +3477,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3603,7 +3513,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3611,25 +3521,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="27.1796875" collapsed="true"/>
+    <col min="11" max="11" width="27.1796875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3679,12 +3589,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3701,20 +3611,20 @@
         <v>Smith</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3748,7 +3658,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 10/16/2025,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3756,28 +3666,28 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="22.6328125" collapsed="true"/>
+    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="22.6328125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3827,12 +3737,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3858,11 +3768,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3881,19 +3791,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="19.6328125" collapsed="true"/>
+    <col min="11" max="11" width="19.6328125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3943,12 +3853,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3974,11 +3884,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3997,19 +3907,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="30.54296875" collapsed="true"/>
+    <col min="11" max="11" width="30.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4059,12 +3969,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4090,11 +4000,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4113,19 +4023,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="17.90625" collapsed="true"/>
+    <col min="11" max="11" width="17.90625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4175,12 +4085,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4197,20 +4107,20 @@
         <v>CarlosJacinta</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4242,7 +4152,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4250,25 +4160,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="23.81640625" collapsed="true"/>
+    <col min="11" max="11" width="23.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4318,12 +4228,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4340,20 +4250,20 @@
         <v>Carlos</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4385,7 +4295,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4393,25 +4303,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4461,12 +4371,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4483,20 +4393,20 @@
         <v>Smith</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4530,7 +4440,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4538,25 +4448,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="28.54296875" collapsed="true"/>
+    <col min="11" max="11" width="28.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4606,12 +4516,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4628,20 +4538,20 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>10/16/2025</v>
+        <v>01/05/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4672,7 +4582,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 10/16/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4680,12 +4590,12 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/16/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -1,47 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F17B18-9C53-451E-A1EC-31CAB16A486C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{329EE51D-A7FC-471D-A808-3284C8C5AEBF}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="7" firstSheet="7" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="CVCSPSCFCorp_IPDailyNOP" sheetId="1" r:id="rId1"/>
-    <sheet name="CVCSPSCFCorp_AutomaticPayment" sheetId="2" r:id="rId2"/>
-    <sheet name="CVCSPSCFPC_AutomaticPayment" sheetId="4" r:id="rId3"/>
-    <sheet name="CVCSPSCFPS_AutomaticPayment" sheetId="3" r:id="rId4"/>
-    <sheet name="CVCSPSCFCC_AutomaticPayment" sheetId="5" r:id="rId5"/>
-    <sheet name="CVCSPSCFPS_RecDeferred" sheetId="6" r:id="rId6"/>
-    <sheet name="CVCSPSCFPC_RecDeferred" sheetId="7" r:id="rId7"/>
-    <sheet name="CVCSPSCFCorp_RecDeferred" sheetId="8" r:id="rId8"/>
-    <sheet name="CVCSPSCFCC_RecDeferred" sheetId="9" r:id="rId9"/>
-    <sheet name="CVCSPSCFPS_RecDaily" sheetId="10" r:id="rId10"/>
-    <sheet name="CVCSPSCFPC_RecDaily" sheetId="11" r:id="rId11"/>
-    <sheet name="CVCSPSCFCorp_RecDaily" sheetId="12" r:id="rId12"/>
-    <sheet name="CVCSPSCFCC_RecDaily" sheetId="13" r:id="rId13"/>
-    <sheet name="CVCSPSCFPS_IPDeferred" sheetId="14" r:id="rId14"/>
-    <sheet name="CVCSPSCFPC_IPDeferred" sheetId="15" r:id="rId15"/>
-    <sheet name="CVCSPSCFCC_IPDeferred" sheetId="16" r:id="rId16"/>
-    <sheet name="CVCSPSCFCorp_IPDeferred" sheetId="17" r:id="rId17"/>
-    <sheet name="CVCSPSCFPS_IPDailyIA" sheetId="18" r:id="rId18"/>
-    <sheet name="CVCSPSCFPC_IPDailyIA" sheetId="19" r:id="rId19"/>
-    <sheet name="CVCSPSCFCC_IPDailyIA" sheetId="20" r:id="rId20"/>
-    <sheet name="CVCSPSCFCorp_IPDailyIA" sheetId="21" r:id="rId21"/>
-    <sheet name="CVCSPSCFCC_IPDailyNOP" sheetId="22" r:id="rId22"/>
-    <sheet name="CVCSPSCFPC_IPDailyNOP" sheetId="23" r:id="rId23"/>
-    <sheet name="CVCSPSCFPS_IPDailyNOP" sheetId="24" r:id="rId24"/>
-    <sheet name="CVCSPSCFCorp_RecMonthly" sheetId="25" r:id="rId25"/>
+    <sheet name="CVCSPSCFCorp_IPDailyNOP" r:id="rId1" sheetId="1"/>
+    <sheet name="CVCSPSCFCorp_AutomaticPayment" r:id="rId2" sheetId="2"/>
+    <sheet name="CVCSPSCFPC_AutomaticPayment" r:id="rId3" sheetId="4"/>
+    <sheet name="CVCSPSCFPS_AutomaticPayment" r:id="rId4" sheetId="3"/>
+    <sheet name="CVCSPSCFCC_AutomaticPayment" r:id="rId5" sheetId="5"/>
+    <sheet name="CVCSPSCFPS_RecDeferred" r:id="rId6" sheetId="6"/>
+    <sheet name="CVCSPSCFPC_RecDeferred" r:id="rId7" sheetId="7"/>
+    <sheet name="CVCSPSCFCorp_RecDeferred" r:id="rId8" sheetId="8"/>
+    <sheet name="CVCSPSCFCC_RecDeferred" r:id="rId9" sheetId="9"/>
+    <sheet name="CVCSPSCFPS_RecDaily" r:id="rId10" sheetId="10"/>
+    <sheet name="CVCSPSCFPC_RecDaily" r:id="rId11" sheetId="11"/>
+    <sheet name="CVCSPSCFCorp_RecDaily" r:id="rId12" sheetId="12"/>
+    <sheet name="CVCSPSCFCC_RecDaily" r:id="rId13" sheetId="13"/>
+    <sheet name="CVCSPSCFPS_IPDeferred" r:id="rId14" sheetId="14"/>
+    <sheet name="CVCSPSCFPC_IPDeferred" r:id="rId15" sheetId="15"/>
+    <sheet name="CVCSPSCFCC_IPDeferred" r:id="rId16" sheetId="16"/>
+    <sheet name="CVCSPSCFCorp_IPDeferred" r:id="rId17" sheetId="17"/>
+    <sheet name="CVCSPSCFPS_IPDailyIA" r:id="rId18" sheetId="18"/>
+    <sheet name="CVCSPSCFPC_IPDailyIA" r:id="rId19" sheetId="19"/>
+    <sheet name="CVCSPSCFCC_IPDailyIA" r:id="rId20" sheetId="20"/>
+    <sheet name="CVCSPSCFCorp_IPDailyIA" r:id="rId21" sheetId="21"/>
+    <sheet name="CVCSPSCFCC_IPDailyNOP" r:id="rId22" sheetId="22"/>
+    <sheet name="CVCSPSCFPC_IPDailyNOP" r:id="rId23" sheetId="23"/>
+    <sheet name="CVCSPSCFPS_IPDailyNOP" r:id="rId24" sheetId="24"/>
+    <sheet name="CVCSPSCFCorp_RecMonthly" r:id="rId25" sheetId="25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="75">
   <si>
     <t>Result</t>
   </si>
@@ -270,33 +270,6 @@
 CATAWBA, North Carolina NC 28609,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Terry Foundation,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Business Tax ID:,	999999999,
-Routing Number:,	****4974,
-Account Number:,	****8307,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
@@ -697,9 +670,6 @@
     <t>Fri Dec 26 21:16:43 IST 2025</t>
   </si>
   <si>
-    <t>Fri Dec 26 21:18:09 IST 2025</t>
-  </si>
-  <si>
     <t>Fri Dec 26 21:19:35 IST 2025</t>
   </si>
   <si>
@@ -737,6 +707,44 @@
   </si>
   <si>
     <t>Fri Dec 26 21:37:24 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:04:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+180RemittanceID: 917-152027,
+1. Review bill to pay,
+Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+ImtiazABPsingleCFBills,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+Company Name:,	Terry Foundation,
+First Name:,	CAROLYN,
+Last Name:,	LINEBERGER,
+Routing Number:,	****4974,
+Account Number:,	****8307,
+Billing Address:,	7072 MAPLE GLEN DR,
+CATAWBA, North Carolina NC 28609
+Country:,	UNITED STATES,
+Account Type:,	Business Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:15:25 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -805,46 +813,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="164" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="2" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -861,10 +869,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -899,7 +907,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -934,7 +942,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1028,21 +1036,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1059,7 +1067,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1111,22 +1119,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="23.6328125" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="30.26953125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" customWidth="true" width="23.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="30.26953125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,12 +1184,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1207,11 +1215,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1245,7 +1253,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1253,13 +1261,13 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1267,14 +1275,14 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="26.08984375" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="26.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1324,12 +1332,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1355,11 +1363,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1391,7 +1399,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/10/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1399,25 +1407,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="25.7265625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="25.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,12 +1475,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1498,11 +1506,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1534,7 +1542,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/10/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1542,25 +1550,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="30.7265625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="30.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1610,12 +1618,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1641,11 +1649,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1679,7 +1687,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/10/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1687,25 +1695,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="34.7265625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="34.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1755,12 +1763,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1786,11 +1794,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1821,7 +1829,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/10/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1829,27 +1837,27 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="24.7265625" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="15.7265625" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="17.1796875" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" width="15.7265625" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" width="17.1796875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row ht="29" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,12 +1907,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1930,11 +1938,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1966,7 +1974,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1974,25 +1982,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="24.26953125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="24.26953125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2042,12 +2050,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2073,11 +2081,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2109,7 +2117,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2117,25 +2125,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="23.7265625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="23.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2185,12 +2193,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2216,11 +2224,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2251,7 +2259,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2259,25 +2267,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="25.81640625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="25.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2327,12 +2335,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2358,11 +2366,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2396,7 +2404,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2404,25 +2412,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="24" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="24.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2472,12 +2480,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2500,14 +2508,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2539,7 +2547,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2547,25 +2555,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="23.08984375" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="23.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2615,12 +2623,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2643,14 +2651,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2682,7 +2690,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2690,25 +2698,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="21.90625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="21.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2758,12 +2766,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2793,7 +2801,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2812,19 +2820,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="21.81640625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2874,12 +2882,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2902,14 +2910,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2940,7 +2948,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2948,25 +2956,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="20.36328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3016,12 +3024,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3044,14 +3052,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3085,7 +3093,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3093,25 +3101,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="27.08984375" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="27.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3161,12 +3169,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3192,11 +3200,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3227,7 +3235,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3235,25 +3243,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="29" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="29.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3303,12 +3311,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3334,11 +3342,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3370,7 +3378,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3378,25 +3386,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="29.90625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3446,12 +3454,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3477,11 +3485,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3513,7 +3521,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3521,25 +3529,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="27.1796875" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="27.1796875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3589,12 +3597,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3614,17 +3622,17 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3658,7 +3666,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 01/10/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3666,28 +3674,28 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="22.6328125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="22.6328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3737,12 +3745,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3772,7 +3780,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3791,19 +3799,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="19.6328125" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="19.6328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3853,12 +3861,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3888,7 +3896,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3907,19 +3915,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="30.54296875" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="30.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3969,12 +3977,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4004,7 +4012,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4023,19 +4031,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="17.90625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="17.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4085,12 +4093,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4120,7 +4128,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4152,7 +4160,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4160,25 +4168,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="23.81640625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="23.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4228,12 +4236,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4263,7 +4271,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4295,7 +4303,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4303,25 +4311,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="21.81640625" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4371,12 +4379,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4402,11 +4410,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4429,7 +4437,6 @@
 Company Name:,	Terry Foundation,
 First Name:,	CAROLYN,
 Last Name:,	LINEBERGER,
-Business Tax ID:,	999999999,
 Routing Number:,	****4974,
 Account Number:,	****8307,
 Billing Address:,	7072 MAPLE GLEN DR,
@@ -4440,7 +4447,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4448,25 +4455,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="28.54296875" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" customWidth="true" width="28.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4516,12 +4523,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4547,11 +4554,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/10/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4582,7 +4589,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/10/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4590,12 +4597,12 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/10/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="101">
   <si>
     <t>Result</t>
   </si>
@@ -745,6 +745,84 @@
   </si>
   <si>
     <t>Fri Jan 09 18:15:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:32:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:33:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:34:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:35:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:36:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:38:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:39:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:43:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:44:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:46:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:47:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:48:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:49:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:51:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:53:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:55:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:58:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 03:59:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:01:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:30:50 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1337,7 +1415,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1480,7 +1558,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1623,7 +1701,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1768,7 +1846,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1912,7 +1990,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2055,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2198,7 +2276,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2340,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2485,7 +2563,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2628,7 +2706,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2771,7 +2849,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2887,7 +2965,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3029,7 +3107,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3174,7 +3252,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3316,7 +3394,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3459,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3602,7 +3680,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3750,7 +3828,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3866,7 +3944,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3982,7 +4060,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4098,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4241,7 +4319,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4384,7 +4462,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4528,7 +4606,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="127">
   <si>
     <t>Result</t>
   </si>
@@ -823,6 +823,84 @@
   </si>
   <si>
     <t>Wed Mar 11 00:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:50:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:55:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:03:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:04:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:06:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:07:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:08:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:09:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:14:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:17:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:20:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:21:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:23:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1345,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1415,7 +1493,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1558,7 +1636,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1701,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1846,7 +1924,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1990,7 +2068,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2133,7 +2211,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2276,7 +2354,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2418,7 +2496,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2563,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2706,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2849,7 +2927,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2965,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3107,7 +3185,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3252,7 +3330,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3394,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3537,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3680,7 +3758,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3828,7 +3906,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3944,7 +4022,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4060,7 +4138,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4176,7 +4254,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4319,7 +4397,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4462,7 +4540,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4606,7 +4684,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="142">
   <si>
     <t>Result</t>
   </si>
@@ -901,6 +901,51 @@
   </si>
   <si>
     <t>Tue Jun 02 12:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:41:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 21:49:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:02:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:04:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:07:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:10:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:17:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:32:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:40:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:46:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:54:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:57:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:00:33 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1390,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1779,7 +1824,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1924,7 +1969,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2496,7 +2541,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2641,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2784,7 +2829,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3185,7 +3230,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3758,7 +3803,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3906,7 +3951,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4397,7 +4442,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="190">
   <si>
     <t>Result</t>
   </si>
@@ -946,6 +946,150 @@
   </si>
   <si>
     <t>Mon Jun 08 22:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:35:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:37:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:39:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:42:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:44:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:45:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:47:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:49:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:52:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:54:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:55:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:58:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:59:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:02:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:04:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:05:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:07:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:09:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:10:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:12:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:53:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:54:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:11:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:14:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:17:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:19:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:21:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:22:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:28:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:31:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:32:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:34:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:37:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:40:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:48:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 13:51:51 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1534,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1538,7 +1682,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1681,7 +1825,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1824,7 +1968,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1969,7 +2113,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2113,7 +2257,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2256,7 +2400,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2399,7 +2543,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2541,7 +2685,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2686,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2829,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2972,7 +3116,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3088,7 +3232,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3230,7 +3374,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3375,7 +3519,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3517,7 +3661,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3660,7 +3804,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3803,7 +3947,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3951,7 +4095,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4067,7 +4211,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4183,7 +4327,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4299,7 +4443,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4442,7 +4586,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4585,7 +4729,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4729,7 +4873,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="215">
   <si>
     <t>Result</t>
   </si>
@@ -1090,6 +1090,81 @@
   </si>
   <si>
     <t>Fri Jun 19 13:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:11:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:12:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:15:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:17:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:19:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:20:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:21:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:22:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:23:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:25:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:26:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:27:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:30:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:34:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:35:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:38:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:41:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="23.6328125" collapsed="true"/>
@@ -1501,13 +1576,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1530,11 +1605,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>173</v>
+      <c r="B2" t="s" s="0">
+        <v>198</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1546,17 +1621,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1621,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="26.08984375" collapsed="true"/>
@@ -1649,13 +1724,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1678,11 +1753,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>189</v>
+      <c r="B2" t="s" s="0">
+        <v>213</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1694,17 +1769,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1764,7 +1839,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.7265625" collapsed="true"/>
@@ -1792,13 +1867,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1821,11 +1896,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>181</v>
+      <c r="B2" t="s" s="0">
+        <v>207</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1837,17 +1912,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1907,7 +1982,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.7265625" collapsed="true"/>
@@ -1935,13 +2010,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1964,11 +2039,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>175</v>
+      <c r="B2" t="s" s="0">
+        <v>200</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1980,17 +2055,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2052,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="34.7265625" collapsed="true"/>
@@ -2080,13 +2155,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2109,11 +2184,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>170</v>
+      <c r="B2" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2125,17 +2200,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2194,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
@@ -2224,13 +2299,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2253,11 +2328,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>185</v>
+      <c r="B2" t="s" s="0">
+        <v>212</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2269,17 +2344,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2339,7 +2414,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.26953125" collapsed="true"/>
@@ -2367,13 +2442,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2396,11 +2471,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>180</v>
+      <c r="B2" t="s" s="0">
+        <v>206</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2412,17 +2487,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2482,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.7265625" collapsed="true"/>
@@ -2510,13 +2585,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2539,11 +2614,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>169</v>
+      <c r="B2" t="s" s="0">
+        <v>193</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2555,17 +2630,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2624,7 +2699,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.81640625" collapsed="true"/>
@@ -2652,13 +2727,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2681,11 +2756,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>174</v>
+      <c r="B2" t="s" s="0">
+        <v>199</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2697,17 +2772,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2769,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.0" collapsed="true"/>
@@ -2797,13 +2872,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2826,11 +2901,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>188</v>
+      <c r="B2" t="s" s="0">
+        <v>210</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2842,17 +2917,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2912,7 +2987,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.08984375" collapsed="true"/>
@@ -2940,13 +3015,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2969,11 +3044,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>178</v>
+      <c r="B2" t="s" s="0">
+        <v>204</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2985,17 +3060,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3055,7 +3130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.90625" collapsed="true"/>
@@ -3083,13 +3158,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3112,11 +3187,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>148</v>
+      <c r="B2" t="s" s="0">
+        <v>196</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3128,17 +3203,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3171,7 +3246,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
@@ -3199,13 +3274,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3228,11 +3303,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>143</v>
+      <c r="B2" t="s" s="0">
+        <v>191</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3244,17 +3319,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3313,7 +3388,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
@@ -3341,13 +3416,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3370,11 +3445,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>172</v>
+      <c r="B2" t="s" s="0">
+        <v>197</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3386,17 +3461,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3458,7 +3533,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.08984375" collapsed="true"/>
@@ -3486,13 +3561,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3515,11 +3590,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>168</v>
+      <c r="B2" t="s" s="0">
+        <v>192</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3531,17 +3606,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3600,7 +3675,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.0" collapsed="true"/>
@@ -3628,13 +3703,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3657,11 +3732,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>179</v>
+      <c r="B2" t="s" s="0">
+        <v>205</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3673,17 +3748,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3743,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
@@ -3771,13 +3846,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3800,11 +3875,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>184</v>
+      <c r="B2" t="s" s="0">
+        <v>211</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3816,17 +3891,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3886,7 +3961,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.1796875" collapsed="true"/>
@@ -3914,13 +3989,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3943,11 +4018,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>177</v>
+      <c r="B2" t="s" s="0">
+        <v>202</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3959,17 +4034,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4031,7 +4106,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
@@ -4062,13 +4137,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4091,11 +4166,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>155</v>
+      <c r="B2" t="s" s="0">
+        <v>203</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4107,17 +4182,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4150,7 +4225,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="19.6328125" collapsed="true"/>
@@ -4178,13 +4253,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4207,11 +4282,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>161</v>
+      <c r="B2" t="s" s="0">
+        <v>209</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4223,17 +4298,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4266,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.54296875" collapsed="true"/>
@@ -4294,13 +4369,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4323,11 +4398,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>167</v>
+      <c r="B2" t="s" s="0">
+        <v>190</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4339,17 +4414,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4382,7 +4457,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="17.90625" collapsed="true"/>
@@ -4410,13 +4485,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4439,11 +4514,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>187</v>
+      <c r="B2" t="s" s="0">
+        <v>214</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4455,17 +4530,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4525,7 +4600,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.81640625" collapsed="true"/>
@@ -4553,13 +4628,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4582,11 +4657,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>182</v>
+      <c r="B2" t="s" s="0">
+        <v>208</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4598,17 +4673,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4668,7 +4743,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
@@ -4696,13 +4771,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4725,11 +4800,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>176</v>
+      <c r="B2" t="s" s="0">
+        <v>201</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4741,17 +4816,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4812,7 +4887,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="28.54296875" collapsed="true"/>
@@ -4840,13 +4915,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4869,11 +4944,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>171</v>
+      <c r="B2" t="s" s="0">
+        <v>195</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4885,17 +4960,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="240">
   <si>
     <t>Result</t>
   </si>
@@ -1165,6 +1165,81 @@
   </si>
   <si>
     <t>Sat Aug 08 20:41:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:20:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:21:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:22:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:23:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:24:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:25:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:26:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:27:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:29:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:31:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:32:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:33:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:37:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:38:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:40:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:43:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:45:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:46:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:47:41 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1684,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1757,7 +1832,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1900,7 +1975,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2043,7 +2118,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2188,7 +2263,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2332,7 +2407,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2475,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2618,7 +2693,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2760,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2905,7 +2980,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3048,7 +3123,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3191,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3307,7 +3382,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3449,7 +3524,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3594,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3736,7 +3811,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3879,7 +3954,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4022,7 +4097,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4170,7 +4245,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4286,7 +4361,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4402,7 +4477,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4518,7 +4593,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4661,7 +4736,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4804,7 +4879,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4948,7 +5023,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
